--- a/backend/src/db/demo-docs/measurements-hooded-tank.xlsx
+++ b/backend/src/db/demo-docs/measurements-hooded-tank.xlsx
@@ -749,19 +749,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>33.5</v>
       </c>
     </row>
@@ -778,19 +781,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>23</v>
       </c>
     </row>
@@ -807,19 +813,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>9.5</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>10.5</v>
       </c>
     </row>
